--- a/输入股票代码及名称清单v1.xlsx
+++ b/输入股票代码及名称清单v1.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\13811\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED47A27-8598-46E1-87A7-7067DAFC4409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="11055"/>
+    <workbookView xWindow="1808" yWindow="1808" windowWidth="17999" windowHeight="10432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -22,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="297">
   <si>
     <t>股票代码</t>
   </si>
@@ -45,30 +49,6 @@
     <t>蔚蓝锂芯</t>
   </si>
   <si>
-    <t>SZ002594</t>
-  </si>
-  <si>
-    <t>比亚迪</t>
-  </si>
-  <si>
-    <t>SZ301339</t>
-  </si>
-  <si>
-    <t>通行宝</t>
-  </si>
-  <si>
-    <t>SZ001278</t>
-  </si>
-  <si>
-    <t>一彬科技</t>
-  </si>
-  <si>
-    <t>SZ001366</t>
-  </si>
-  <si>
-    <t>播恩集团</t>
-  </si>
-  <si>
     <t>SZ002460</t>
   </si>
   <si>
@@ -105,12 +85,6 @@
     <t>派瑞股份</t>
   </si>
   <si>
-    <t>SZ002606</t>
-  </si>
-  <si>
-    <t>大连电瓷</t>
-  </si>
-  <si>
     <t>SZ002028</t>
   </si>
   <si>
@@ -123,36 +97,12 @@
     <t>东山精密</t>
   </si>
   <si>
-    <t>SZ001896</t>
-  </si>
-  <si>
-    <t>豫能控股</t>
-  </si>
-  <si>
-    <t>SZ002497</t>
-  </si>
-  <si>
-    <t>雅化集团</t>
-  </si>
-  <si>
     <t>SZ002240</t>
   </si>
   <si>
     <t>盛新锂能</t>
   </si>
   <si>
-    <t>SZ002738</t>
-  </si>
-  <si>
-    <t>中矿资源</t>
-  </si>
-  <si>
-    <t>SZ300503</t>
-  </si>
-  <si>
-    <t>昊志机电</t>
-  </si>
-  <si>
     <t>SZ300885</t>
   </si>
   <si>
@@ -165,150 +115,24 @@
     <t>拓新药业</t>
   </si>
   <si>
-    <t>SZ002252</t>
-  </si>
-  <si>
-    <t>上海莱士</t>
-  </si>
-  <si>
-    <t>SZ300094</t>
-  </si>
-  <si>
-    <t>国联水产</t>
-  </si>
-  <si>
-    <t>SZ000037</t>
-  </si>
-  <si>
-    <t>深南电A</t>
-  </si>
-  <si>
     <t>SZ000919</t>
   </si>
   <si>
     <t>金陵药业</t>
   </si>
   <si>
-    <t>SZ000625</t>
-  </si>
-  <si>
-    <t>长安汽车</t>
-  </si>
-  <si>
-    <t>SZ000651</t>
-  </si>
-  <si>
-    <t>格力电器</t>
-  </si>
-  <si>
-    <t>SZ002352</t>
-  </si>
-  <si>
-    <t>顺丰控股</t>
-  </si>
-  <si>
-    <t>SZ300024</t>
-  </si>
-  <si>
-    <t>机器人</t>
-  </si>
-  <si>
-    <t>SZ000858</t>
-  </si>
-  <si>
-    <t>五 粮 液</t>
-  </si>
-  <si>
-    <t>SZ000568</t>
-  </si>
-  <si>
-    <t>泸州老窖</t>
-  </si>
-  <si>
-    <t>SZ002304</t>
-  </si>
-  <si>
-    <t>洋河股份</t>
-  </si>
-  <si>
-    <t>SZ000995</t>
-  </si>
-  <si>
-    <t>皇台酒业</t>
-  </si>
-  <si>
     <t>SZ002791</t>
   </si>
   <si>
     <t>坚朗五金</t>
   </si>
   <si>
-    <t>SZ301046</t>
-  </si>
-  <si>
-    <t>能辉科技</t>
-  </si>
-  <si>
     <t>SZ002402</t>
   </si>
   <si>
     <t>和而泰</t>
   </si>
   <si>
-    <t>SZ002942</t>
-  </si>
-  <si>
-    <t>新农股份</t>
-  </si>
-  <si>
-    <t>SZ002333</t>
-  </si>
-  <si>
-    <t>罗普斯金</t>
-  </si>
-  <si>
-    <t>SZ001368</t>
-  </si>
-  <si>
-    <t>通达创智</t>
-  </si>
-  <si>
-    <t>SZ002011</t>
-  </si>
-  <si>
-    <t>盾安环境</t>
-  </si>
-  <si>
-    <t>SZ301197</t>
-  </si>
-  <si>
-    <t>工大科雅</t>
-  </si>
-  <si>
-    <t>SZ000707</t>
-  </si>
-  <si>
-    <t>双环科技</t>
-  </si>
-  <si>
-    <t>SZ300432</t>
-  </si>
-  <si>
-    <t>富临精工</t>
-  </si>
-  <si>
-    <t>SZ002125</t>
-  </si>
-  <si>
-    <t>湘潭电化</t>
-  </si>
-  <si>
-    <t>SZ300769</t>
-  </si>
-  <si>
-    <t>德方纳米</t>
-  </si>
-  <si>
     <t>SZ300207</t>
   </si>
   <si>
@@ -339,24 +163,12 @@
     <t>立讯精密</t>
   </si>
   <si>
-    <t>SZ000559</t>
-  </si>
-  <si>
-    <t>万向钱潮</t>
-  </si>
-  <si>
     <t>SZ002241</t>
   </si>
   <si>
     <t>歌尔股份</t>
   </si>
   <si>
-    <t>SZ159796</t>
-  </si>
-  <si>
-    <t>电池ETF汇添富</t>
-  </si>
-  <si>
     <t>SZ002271</t>
   </si>
   <si>
@@ -375,12 +187,6 @@
     <t>宁德时代</t>
   </si>
   <si>
-    <t>SZ002342</t>
-  </si>
-  <si>
-    <t>巨力索具</t>
-  </si>
-  <si>
     <t>SZ300442</t>
   </si>
   <si>
@@ -399,12 +205,6 @@
     <t>中伟新材</t>
   </si>
   <si>
-    <t>SZ300619</t>
-  </si>
-  <si>
-    <t>金银河</t>
-  </si>
-  <si>
     <t>SZ300274</t>
   </si>
   <si>
@@ -417,84 +217,24 @@
     <t>天赐材料</t>
   </si>
   <si>
-    <t>SZ002759</t>
-  </si>
-  <si>
-    <t>天际股份</t>
-  </si>
-  <si>
-    <t>SZ002009</t>
-  </si>
-  <si>
-    <t>天奇股份</t>
-  </si>
-  <si>
-    <t>SZ300450</t>
-  </si>
-  <si>
-    <t>先导智能</t>
-  </si>
-  <si>
-    <t>SZ002372</t>
-  </si>
-  <si>
-    <t>伟星新材</t>
-  </si>
-  <si>
-    <t>SZ159736</t>
-  </si>
-  <si>
-    <t>食品饮料ETF天弘</t>
-  </si>
-  <si>
     <t>SZ001386</t>
   </si>
   <si>
     <t>马可波罗</t>
   </si>
   <si>
-    <t>SZ000632</t>
-  </si>
-  <si>
-    <t>三木集团</t>
-  </si>
-  <si>
     <t>SZ000657</t>
   </si>
   <si>
     <t>中钨高新</t>
   </si>
   <si>
-    <t>SZ002120</t>
-  </si>
-  <si>
-    <t>韵达股份</t>
-  </si>
-  <si>
-    <t>SZ002021</t>
-  </si>
-  <si>
-    <t>中捷资源</t>
-  </si>
-  <si>
-    <t>SZ002266</t>
-  </si>
-  <si>
-    <t>浙富控股</t>
-  </si>
-  <si>
     <t>SZ300760</t>
   </si>
   <si>
     <t>迈瑞医疗</t>
   </si>
   <si>
-    <t>SZ300479</t>
-  </si>
-  <si>
-    <t>神思电子</t>
-  </si>
-  <si>
     <t>SZ300558</t>
   </si>
   <si>
@@ -507,12 +247,6 @@
     <t>北大医药</t>
   </si>
   <si>
-    <t>SZ002552</t>
-  </si>
-  <si>
-    <t>宝鼎科技</t>
-  </si>
-  <si>
     <t>SZ300404</t>
   </si>
   <si>
@@ -531,30 +265,6 @@
     <t>润和软件</t>
   </si>
   <si>
-    <t>SZ300496</t>
-  </si>
-  <si>
-    <t>中科创达</t>
-  </si>
-  <si>
-    <t>SZ300058</t>
-  </si>
-  <si>
-    <t>蓝色光标</t>
-  </si>
-  <si>
-    <t>SZ301066</t>
-  </si>
-  <si>
-    <t>万事利</t>
-  </si>
-  <si>
-    <t>SZ000596</t>
-  </si>
-  <si>
-    <t>古井贡酒</t>
-  </si>
-  <si>
     <t>SZ002202</t>
   </si>
   <si>
@@ -567,70 +277,10 @@
     <t>许继电气</t>
   </si>
   <si>
-    <t>SZ301049</t>
-  </si>
-  <si>
-    <t>超越科技</t>
-  </si>
-  <si>
     <t>SZ002866</t>
   </si>
   <si>
     <t>传艺科技</t>
-  </si>
-  <si>
-    <t>SZ001330</t>
-  </si>
-  <si>
-    <t>博纳影业</t>
-  </si>
-  <si>
-    <t>SZ000977</t>
-  </si>
-  <si>
-    <t>浪潮信息</t>
-  </si>
-  <si>
-    <t>SZ002230</t>
-  </si>
-  <si>
-    <t>科大讯飞</t>
-  </si>
-  <si>
-    <t>SZ002990</t>
-  </si>
-  <si>
-    <t>盛视科技</t>
-  </si>
-  <si>
-    <t>SZ001230</t>
-  </si>
-  <si>
-    <t>劲旅环境</t>
-  </si>
-  <si>
-    <t>SZ300327</t>
-  </si>
-  <si>
-    <t>中颖电子</t>
-  </si>
-  <si>
-    <t>SZ002215</t>
-  </si>
-  <si>
-    <t>诺 普 信</t>
-  </si>
-  <si>
-    <t>SZ301602</t>
-  </si>
-  <si>
-    <t>超研股份</t>
-  </si>
-  <si>
-    <t>SZ000983</t>
-  </si>
-  <si>
-    <t>山西焦煤</t>
   </si>
   <si>
     <t>序号</t>
@@ -1281,14 +931,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1301,6 +945,7 @@
       <sz val="6"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1308,349 +953,27 @@
       <sz val="6"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1673,255 +996,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1937,93 +1018,159 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -2034,7 +1181,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2062,154 +1209,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2459,20 +1492,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B100"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.9557522123894" customWidth="1"/>
-    <col min="2" max="2" width="20.2477876106195" customWidth="1"/>
+    <col min="1" max="1" width="12.9296875" customWidth="1"/>
+    <col min="2" max="2" width="18.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2480,914 +1513,433 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="5" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="5" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="5" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="5" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="5" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="5" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="5" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="5" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="5" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="5" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="5" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="5" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="5" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="5" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="5" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="5" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="5" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="5" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="5" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="5" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="5" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="5" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="5" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="5" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="5" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="5" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="5" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="5" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="5" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="5" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="5" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G101"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="12" customHeight="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="19.716814159292" customWidth="1"/>
+    <col min="7" max="7" width="19.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:7">
+    <row r="1" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>202</v>
+        <v>84</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>203</v>
+        <v>85</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>204</v>
+        <v>86</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>206</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>207</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2">
         <v>3828.65</v>
       </c>
       <c r="E2" s="3">
-        <v>0.0245</v>
+        <v>2.4500000000000001E-2</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:7">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2">
         <v>2354.67</v>
       </c>
       <c r="E3" s="3">
-        <v>0.0965</v>
+        <v>9.6500000000000002E-2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>211</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="D4" s="2">
         <v>1878.52</v>
       </c>
       <c r="E4" s="3">
-        <v>0.1614</v>
+        <v>0.16139999999999999</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>214</v>
+        <v>96</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>215</v>
+        <v>97</v>
       </c>
       <c r="D5" s="2">
         <v>1197.74</v>
@@ -3396,90 +1948,90 @@
         <v>0.2351</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2">
         <v>915.75</v>
       </c>
       <c r="E6" s="3">
-        <v>0.1127</v>
+        <v>0.11269999999999999</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2">
-        <v>1103.36</v>
+        <v>1103.3599999999999</v>
       </c>
       <c r="E7" s="3">
-        <v>0.2945</v>
+        <v>0.29449999999999998</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>219</v>
+        <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2">
         <v>417.44</v>
       </c>
       <c r="E8" s="3">
-        <v>0.1513</v>
+        <v>0.15129999999999999</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>222</v>
+        <v>104</v>
       </c>
       <c r="D9" s="2">
         <v>425.36</v>
@@ -3488,90 +2040,90 @@
         <v>0.123</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>224</v>
+        <v>106</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>225</v>
+        <v>107</v>
       </c>
       <c r="D10" s="2">
         <v>238.25</v>
       </c>
       <c r="E10" s="3">
-        <v>0.4391</v>
+        <v>0.43909999999999999</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>227</v>
+        <v>109</v>
       </c>
       <c r="D11" s="2">
         <v>409.78</v>
       </c>
       <c r="E11" s="3">
-        <v>0.2146</v>
+        <v>0.21460000000000001</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>228</v>
+        <v>110</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>229</v>
+        <v>111</v>
       </c>
       <c r="D12" s="2">
         <v>488.62</v>
       </c>
       <c r="E12" s="3">
-        <v>0.2978</v>
+        <v>0.29780000000000001</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>232</v>
+        <v>114</v>
       </c>
       <c r="D13" s="2">
         <v>1429.02</v>
@@ -3580,136 +2132,136 @@
         <v>0.254</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>233</v>
+        <v>115</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>235</v>
+        <v>117</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>236</v>
+        <v>118</v>
       </c>
       <c r="D14" s="2">
         <v>308.7</v>
       </c>
       <c r="E14" s="3">
-        <v>0.4633</v>
+        <v>0.46329999999999999</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>238</v>
+        <v>120</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>239</v>
+        <v>121</v>
       </c>
       <c r="D15" s="2">
         <v>359.06</v>
       </c>
       <c r="E15" s="3">
-        <v>0.1947</v>
+        <v>0.19470000000000001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>240</v>
+        <v>122</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>241</v>
+        <v>123</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>242</v>
+        <v>124</v>
       </c>
       <c r="D16" s="2">
-        <v>317.1</v>
+        <v>317.10000000000002</v>
       </c>
       <c r="E16" s="3">
-        <v>0.1776</v>
+        <v>0.17760000000000001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>243</v>
+        <v>125</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>244</v>
+        <v>126</v>
       </c>
       <c r="D17" s="2">
         <v>889.16</v>
       </c>
       <c r="E17" s="3">
-        <v>0.1292</v>
+        <v>0.12920000000000001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>245</v>
+        <v>127</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>246</v>
+        <v>128</v>
       </c>
       <c r="D18" s="2">
         <v>674.56</v>
       </c>
       <c r="E18" s="3">
-        <v>0.2134</v>
+        <v>0.21340000000000001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>247</v>
+        <v>129</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>248</v>
+        <v>130</v>
       </c>
       <c r="D19" s="2">
         <v>207.16</v>
@@ -3718,44 +2270,44 @@
         <v>0.3674</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:7">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>251</v>
+        <v>133</v>
       </c>
       <c r="D20" s="2">
         <v>1690.34</v>
       </c>
       <c r="E20" s="3">
-        <v>0.2682</v>
+        <v>0.26819999999999999</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>252</v>
+        <v>134</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>253</v>
+        <v>135</v>
       </c>
       <c r="D21" s="2">
         <v>342.24</v>
@@ -3764,90 +2316,90 @@
         <v>0.3957</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D22" s="2">
         <v>305.83</v>
       </c>
       <c r="E22" s="3">
-        <v>0.1604</v>
+        <v>0.16039999999999999</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>256</v>
+        <v>138</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>257</v>
+        <v>139</v>
       </c>
       <c r="D23" s="2">
-        <v>300.29</v>
+        <v>300.29000000000002</v>
       </c>
       <c r="E23" s="3">
-        <v>0.2076</v>
+        <v>0.20760000000000001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>258</v>
+        <v>140</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>259</v>
+        <v>141</v>
       </c>
       <c r="D24" s="2">
         <v>416.87</v>
       </c>
       <c r="E24" s="3">
-        <v>0.2538</v>
+        <v>0.25380000000000003</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>261</v>
+        <v>143</v>
       </c>
       <c r="D25" s="2">
         <v>775.78</v>
@@ -3856,21 +2408,21 @@
         <v>0.1303</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>264</v>
+        <v>146</v>
       </c>
       <c r="D26" s="2">
         <v>267.42</v>
@@ -3879,136 +2431,136 @@
         <v>0.1951</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>266</v>
+        <v>148</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>267</v>
+        <v>149</v>
       </c>
       <c r="D27" s="2">
         <v>294.88</v>
       </c>
       <c r="E27" s="3">
-        <v>0.2285</v>
+        <v>0.22850000000000001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>268</v>
+        <v>150</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>269</v>
+        <v>151</v>
       </c>
       <c r="D28" s="2">
         <v>361.8</v>
       </c>
       <c r="E28" s="3">
-        <v>0.1884</v>
+        <v>0.18840000000000001</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>270</v>
+        <v>152</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="D29" s="2">
         <v>228.6</v>
       </c>
       <c r="E29" s="3">
-        <v>0.043</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>272</v>
+        <v>154</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>273</v>
+        <v>155</v>
       </c>
       <c r="D30" s="2">
         <v>564.02</v>
       </c>
       <c r="E30" s="3">
-        <v>0.099</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>274</v>
+        <v>156</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>275</v>
+        <v>157</v>
       </c>
       <c r="D31" s="2">
-        <v>290.96</v>
+        <v>290.95999999999998</v>
       </c>
       <c r="E31" s="3">
-        <v>0.1267</v>
+        <v>0.12670000000000001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>276</v>
+        <v>158</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>277</v>
+        <v>159</v>
       </c>
       <c r="D32" s="2">
         <v>497.88</v>
@@ -4017,21 +2569,21 @@
         <v>0.1389</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>278</v>
+        <v>160</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>279</v>
+        <v>161</v>
       </c>
       <c r="D33" s="2">
         <v>404.2</v>
@@ -4040,297 +2592,297 @@
         <v>0.1363</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="D34" s="2">
         <v>362.94</v>
       </c>
       <c r="E34" s="3">
-        <v>0.4029</v>
+        <v>0.40289999999999998</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>280</v>
+        <v>162</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>281</v>
+        <v>163</v>
       </c>
       <c r="D35" s="2">
         <v>209.62</v>
       </c>
       <c r="E35" s="3">
-        <v>0.3205</v>
+        <v>0.32050000000000001</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>282</v>
+        <v>164</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>283</v>
+        <v>165</v>
       </c>
       <c r="D36" s="2">
         <v>238.11</v>
       </c>
       <c r="E36" s="3">
-        <v>0.2988</v>
+        <v>0.29880000000000001</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>284</v>
+        <v>166</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c r="D37" s="2">
         <v>171.04</v>
       </c>
       <c r="E37" s="3">
-        <v>0.9709</v>
+        <v>0.97089999999999999</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>286</v>
+        <v>168</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>287</v>
+        <v>169</v>
       </c>
       <c r="D38" s="2">
         <v>132.19</v>
       </c>
       <c r="E38" s="3">
-        <v>0.1979</v>
+        <v>0.19789999999999999</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>288</v>
+        <v>170</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="D39" s="2">
         <v>148.99</v>
       </c>
       <c r="E39" s="3">
-        <v>0.2181</v>
+        <v>0.21809999999999999</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>291</v>
+        <v>173</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>292</v>
+        <v>174</v>
       </c>
       <c r="D40" s="2">
-        <v>134.42</v>
+        <v>134.41999999999999</v>
       </c>
       <c r="E40" s="3">
         <v>0.1308</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>293</v>
+        <v>175</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>294</v>
+        <v>176</v>
       </c>
       <c r="D41" s="2">
         <v>179.2</v>
       </c>
       <c r="E41" s="3">
-        <v>0.3227</v>
+        <v>0.32269999999999999</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>151</v>
+        <v>65</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="D42" s="2">
         <v>164.34</v>
       </c>
       <c r="E42" s="3">
-        <v>0.6311</v>
+        <v>0.63109999999999999</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>295</v>
+        <v>177</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>296</v>
+        <v>178</v>
       </c>
       <c r="D43" s="2">
         <v>170.98</v>
       </c>
       <c r="E43" s="3">
-        <v>0.2803</v>
+        <v>0.28029999999999999</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="1:7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>297</v>
+        <v>179</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>298</v>
+        <v>180</v>
       </c>
       <c r="D44" s="2">
-        <v>130.33</v>
+        <v>130.33000000000001</v>
       </c>
       <c r="E44" s="3">
         <v>0.3201</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="1:7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>299</v>
+        <v>181</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>300</v>
+        <v>182</v>
       </c>
       <c r="D45" s="2">
         <v>175.55</v>
       </c>
       <c r="E45" s="3">
-        <v>0.3146</v>
+        <v>0.31459999999999999</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>301</v>
+        <v>183</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>302</v>
+        <v>184</v>
       </c>
       <c r="D46" s="2">
         <v>376.98</v>
@@ -4339,90 +2891,90 @@
         <v>0.1229</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>303</v>
+        <v>185</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="D47" s="2">
         <v>1524.41</v>
       </c>
       <c r="E47" s="3">
-        <v>0.5368</v>
+        <v>0.53680000000000005</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="1:7">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>306</v>
+        <v>188</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="D48" s="2">
         <v>802.59</v>
       </c>
       <c r="E48" s="3">
-        <v>0.1876</v>
+        <v>0.18759999999999999</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>308</v>
+        <v>190</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>309</v>
+        <v>191</v>
       </c>
       <c r="D49" s="2">
         <v>130.32</v>
       </c>
       <c r="E49" s="3">
-        <v>0.3021</v>
+        <v>0.30209999999999998</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="1:7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>310</v>
+        <v>192</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>311</v>
+        <v>193</v>
       </c>
       <c r="D50" s="2">
         <v>143.4</v>
@@ -4431,44 +2983,44 @@
         <v>0.4844</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>312</v>
+        <v>194</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>313</v>
+        <v>195</v>
       </c>
       <c r="D51" s="2">
         <v>506.19</v>
       </c>
       <c r="E51" s="3">
-        <v>0.0349</v>
+        <v>3.49E-2</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="1:7">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>314</v>
+        <v>196</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>315</v>
+        <v>197</v>
       </c>
       <c r="D52" s="2">
         <v>364.36</v>
@@ -4477,182 +3029,182 @@
         <v>0.1129</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>316</v>
+        <v>198</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>317</v>
+        <v>199</v>
       </c>
       <c r="D53" s="2">
         <v>320.93</v>
       </c>
       <c r="E53" s="3">
-        <v>0.1592</v>
+        <v>0.15920000000000001</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>318</v>
+        <v>200</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>319</v>
+        <v>201</v>
       </c>
       <c r="D54" s="2">
-        <v>134.95</v>
+        <v>134.94999999999999</v>
       </c>
       <c r="E54" s="3">
         <v>0.2581</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>320</v>
+        <v>202</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>321</v>
+        <v>203</v>
       </c>
       <c r="D55" s="2">
         <v>353.72</v>
       </c>
       <c r="E55" s="3">
-        <v>0.0932</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="1:7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>322</v>
+        <v>204</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>323</v>
+        <v>205</v>
       </c>
       <c r="D56" s="2">
         <v>238.92</v>
       </c>
       <c r="E56" s="3">
-        <v>0.1495</v>
+        <v>0.14949999999999999</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>324</v>
+        <v>206</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>325</v>
+        <v>207</v>
       </c>
       <c r="D57" s="2">
         <v>291.13</v>
       </c>
       <c r="E57" s="3">
-        <v>0.0826</v>
+        <v>8.2600000000000007E-2</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>240</v>
+        <v>122</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>327</v>
+        <v>209</v>
       </c>
       <c r="D58" s="2">
         <v>157.65</v>
       </c>
       <c r="E58" s="3">
-        <v>0.1499</v>
+        <v>0.14990000000000001</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>328</v>
+        <v>210</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>329</v>
+        <v>211</v>
       </c>
       <c r="D59" s="2">
         <v>233.8</v>
       </c>
       <c r="E59" s="3">
-        <v>0.3205</v>
+        <v>0.32050000000000001</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="1:7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>330</v>
+        <v>212</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>331</v>
+        <v>213</v>
       </c>
       <c r="D60" s="2">
         <v>279.52</v>
@@ -4661,44 +3213,44 @@
         <v>0.1091</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>332</v>
+        <v>214</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>333</v>
+        <v>215</v>
       </c>
       <c r="D61" s="2">
         <v>90.07</v>
       </c>
       <c r="E61" s="3">
-        <v>0.3385</v>
+        <v>0.33850000000000002</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="1:7">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>335</v>
+        <v>217</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>336</v>
+        <v>218</v>
       </c>
       <c r="D62" s="2">
         <v>140.29</v>
@@ -4707,21 +3259,21 @@
         <v>0.1106</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>337</v>
+        <v>219</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>338</v>
+        <v>220</v>
       </c>
       <c r="D63" s="2">
         <v>98.87</v>
@@ -4730,67 +3282,67 @@
         <v>0.182</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="1:7">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>340</v>
+        <v>222</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>341</v>
+        <v>223</v>
       </c>
       <c r="D64" s="2">
         <v>104.28</v>
       </c>
       <c r="E64" s="3">
-        <v>0.3424</v>
+        <v>0.34239999999999998</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>342</v>
+        <v>224</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>343</v>
+        <v>225</v>
       </c>
       <c r="D65" s="2">
         <v>206.02</v>
       </c>
       <c r="E65" s="3">
-        <v>0.2358</v>
+        <v>0.23580000000000001</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="1:7">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>345</v>
+        <v>227</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>346</v>
+        <v>228</v>
       </c>
       <c r="D66" s="2">
         <v>85.76</v>
@@ -4799,44 +3351,44 @@
         <v>0.2205</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>347</v>
+        <v>229</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>348</v>
+        <v>230</v>
       </c>
       <c r="D67" s="2">
-        <v>131.55</v>
+        <v>131.55000000000001</v>
       </c>
       <c r="E67" s="3">
         <v>0.1933</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>349</v>
+        <v>231</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>350</v>
+        <v>232</v>
       </c>
       <c r="D68" s="2">
         <v>108.54</v>
@@ -4845,113 +3397,113 @@
         <v>0.1749</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>351</v>
+        <v>233</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>352</v>
+        <v>234</v>
       </c>
       <c r="D69" s="2">
         <v>107.3</v>
       </c>
       <c r="E69" s="3">
-        <v>0.2939</v>
+        <v>0.29389999999999999</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="1:7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>353</v>
+        <v>235</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>354</v>
+        <v>236</v>
       </c>
       <c r="D70" s="2">
         <v>152</v>
       </c>
       <c r="E70" s="3">
-        <v>0.2846</v>
+        <v>0.28460000000000002</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>355</v>
+        <v>237</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>356</v>
+        <v>238</v>
       </c>
       <c r="D71" s="2">
         <v>357.84</v>
       </c>
       <c r="E71" s="3">
-        <v>0.0321</v>
+        <v>3.2099999999999997E-2</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="1:7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>357</v>
+        <v>239</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>358</v>
+        <v>240</v>
       </c>
       <c r="D72" s="2">
         <v>124.25</v>
       </c>
       <c r="E72" s="3">
-        <v>0.2047</v>
+        <v>0.20469999999999999</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="1:7">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>359</v>
+        <v>241</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>360</v>
+        <v>242</v>
       </c>
       <c r="D73" s="2">
         <v>318.95</v>
@@ -4960,90 +3512,90 @@
         <v>0.4612</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>361</v>
+        <v>243</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>362</v>
+        <v>244</v>
       </c>
       <c r="D74" s="2">
         <v>177.83</v>
       </c>
       <c r="E74" s="3">
-        <v>0.3583</v>
+        <v>0.35830000000000001</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>233</v>
+        <v>115</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="1:7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>363</v>
+        <v>245</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>364</v>
+        <v>246</v>
       </c>
       <c r="D75" s="2">
         <v>137.6</v>
       </c>
       <c r="E75" s="3">
-        <v>0.2857</v>
+        <v>0.28570000000000001</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="1:7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>365</v>
+        <v>247</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>366</v>
+        <v>248</v>
       </c>
       <c r="D76" s="2">
         <v>222.68</v>
       </c>
       <c r="E76" s="3">
-        <v>0.2307</v>
+        <v>0.23069999999999999</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="1:7">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>367</v>
+        <v>249</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>368</v>
+        <v>250</v>
       </c>
       <c r="D77" s="2">
         <v>356.29</v>
@@ -5052,90 +3604,90 @@
         <v>0.1138</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>369</v>
+        <v>251</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="D78" s="2">
         <v>80.66</v>
       </c>
       <c r="E78" s="3">
-        <v>0.347</v>
+        <v>0.34699999999999998</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="1:7">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>371</v>
+        <v>253</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>372</v>
+        <v>254</v>
       </c>
       <c r="D79" s="2">
         <v>108.06</v>
       </c>
       <c r="E79" s="3">
-        <v>0.3404</v>
+        <v>0.34039999999999998</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>373</v>
+        <v>255</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>374</v>
+        <v>256</v>
       </c>
       <c r="D80" s="2">
         <v>392.93</v>
       </c>
       <c r="E80" s="3">
-        <v>0.2691</v>
+        <v>0.26910000000000001</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="1:7">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>375</v>
+        <v>257</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>376</v>
+        <v>258</v>
       </c>
       <c r="D81" s="2">
         <v>600.73</v>
@@ -5144,21 +3696,21 @@
         <v>0.1021</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>377</v>
+        <v>259</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>378</v>
+        <v>260</v>
       </c>
       <c r="D82" s="2">
         <v>125.01</v>
@@ -5167,90 +3719,90 @@
         <v>0.2979</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>379</v>
+        <v>261</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>380</v>
+        <v>262</v>
       </c>
       <c r="D83" s="2">
         <v>234.67</v>
       </c>
       <c r="E83" s="3">
-        <v>0.2683</v>
+        <v>0.26829999999999998</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>240</v>
+        <v>122</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" spans="1:7">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>381</v>
+        <v>263</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>382</v>
+        <v>264</v>
       </c>
       <c r="D84" s="2">
         <v>162.94</v>
       </c>
       <c r="E84" s="3">
-        <v>0.4417</v>
+        <v>0.44169999999999998</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>383</v>
+        <v>265</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="D85" s="2">
         <v>130.37</v>
       </c>
       <c r="E85" s="3">
-        <v>0.0679</v>
+        <v>6.7900000000000002E-2</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="D86" s="2">
         <v>234.31</v>
@@ -5259,44 +3811,44 @@
         <v>0.1031</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>385</v>
+        <v>267</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>386</v>
+        <v>268</v>
       </c>
       <c r="D87" s="2">
         <v>98.06</v>
       </c>
       <c r="E87" s="3">
-        <v>0.449</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>387</v>
+        <v>269</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>388</v>
+        <v>270</v>
       </c>
       <c r="D88" s="2">
         <v>120.78</v>
@@ -5305,182 +3857,182 @@
         <v>0.1237</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>389</v>
+        <v>271</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>390</v>
+        <v>272</v>
       </c>
       <c r="D89" s="2">
         <v>117.99</v>
       </c>
       <c r="E89" s="3">
-        <v>0.1322</v>
+        <v>0.13220000000000001</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" spans="1:7">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>391</v>
+        <v>273</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>392</v>
+        <v>274</v>
       </c>
       <c r="D90" s="2">
         <v>76.05</v>
       </c>
       <c r="E90" s="3">
-        <v>0.3443</v>
+        <v>0.34429999999999999</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="1:7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>393</v>
+        <v>275</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="D91" s="2">
         <v>178.84</v>
       </c>
       <c r="E91" s="3">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" spans="1:7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>394</v>
+        <v>276</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>395</v>
+        <v>277</v>
       </c>
       <c r="D92" s="2">
         <v>195.1</v>
       </c>
       <c r="E92" s="3">
-        <v>0.1252</v>
+        <v>0.12520000000000001</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" spans="1:7">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>397</v>
+        <v>279</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>398</v>
+        <v>280</v>
       </c>
       <c r="D93" s="2">
-        <v>301.4</v>
+        <v>301.39999999999998</v>
       </c>
       <c r="E93" s="3">
-        <v>0.0122</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="1:7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>399</v>
+        <v>281</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>400</v>
+        <v>282</v>
       </c>
       <c r="D94" s="2">
         <v>100.15</v>
       </c>
       <c r="E94" s="3">
-        <v>0.4112</v>
+        <v>0.41120000000000001</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="95" customHeight="1" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>401</v>
+        <v>283</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D95" s="2">
         <v>160.5</v>
       </c>
       <c r="E95" s="3">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="96" customHeight="1" spans="1:7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>403</v>
+        <v>285</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>404</v>
+        <v>286</v>
       </c>
       <c r="D96" s="2">
         <v>120.53</v>
@@ -5489,137 +4041,137 @@
         <v>0.4178</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="97" customHeight="1" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>405</v>
+        <v>287</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>406</v>
+        <v>288</v>
       </c>
       <c r="D97" s="2">
         <v>79.47</v>
       </c>
       <c r="E97" s="3">
-        <v>0.4439</v>
+        <v>0.44390000000000002</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>407</v>
+        <v>289</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>408</v>
+        <v>290</v>
       </c>
       <c r="D98" s="2">
         <v>108.08</v>
       </c>
       <c r="E98" s="3">
-        <v>0.1282</v>
+        <v>0.12820000000000001</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" spans="1:7">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>409</v>
+        <v>291</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>410</v>
+        <v>292</v>
       </c>
       <c r="D99" s="2">
         <v>230.25</v>
       </c>
       <c r="E99" s="3">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="1:7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>411</v>
+        <v>293</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>412</v>
+        <v>294</v>
       </c>
       <c r="D100" s="2">
         <v>120.6</v>
       </c>
       <c r="E100" s="3">
-        <v>0.2501</v>
+        <v>0.25009999999999999</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="1:7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>413</v>
+        <v>295</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>414</v>
+        <v>296</v>
       </c>
       <c r="D101" s="2">
         <v>86.6</v>
       </c>
       <c r="E101" s="3">
-        <v>0.137</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>218</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="00992.HK" tooltip="https://00992.hk/"/>
-    <hyperlink ref="C4" r:id="rId2" display="3993.HK" tooltip="https://3993.hk/"/>
-    <hyperlink ref="C26" r:id="rId3" display="9896.HK" tooltip="https://9896.hk/"/>
-    <hyperlink ref="C65" r:id="rId4" display="02313.HK" tooltip="https://02313.hk/"/>
-    <hyperlink ref="C89" r:id="rId5" display="6969.HK" tooltip="https://6969.hk/"/>
-    <hyperlink ref="C93" r:id="rId6" display="01589.HK" tooltip="https://01589.hk/"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="https://00992.hk/" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="C4" r:id="rId2" tooltip="https://3993.hk/" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="C26" r:id="rId3" tooltip="https://9896.hk/" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="C65" r:id="rId4" tooltip="https://02313.hk/" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="C89" r:id="rId5" tooltip="https://6969.hk/" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="C93" r:id="rId6" tooltip="https://01589.hk/" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>